--- a/To-Do.xlsx
+++ b/To-Do.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/94bd72eb5ad3279e/Desktop/Contact App/Contact-App-Quiz/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="11_F25DC773A252ABDACC10487DA91E5B085BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AF9B4ED-DED4-4836-99DA-E737A1BB5E21}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="11_F25DC773A252ABDACC10487DA91E5B085BDE58E8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{56C8EF86-D05C-4FEE-880A-DD1BA6A1FABB}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="20" windowWidth="19180" windowHeight="11260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Make "Add Contact" survive bad age input</t>
   </si>
@@ -61,6 +61,15 @@
   </si>
   <si>
     <t>Cancel option?</t>
+  </si>
+  <si>
+    <t>Add a "category" field to each contact (church, family, work, etc.)</t>
+  </si>
+  <si>
+    <t>Filter contacts by category</t>
+  </si>
+  <si>
+    <t>Show a simple count of contacts per category</t>
   </si>
 </sst>
 </file>
@@ -406,37 +415,56 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:C13"/>
+  <dimension ref="B2:F13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="42" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="55.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>3</v>
       </c>
@@ -444,15 +472,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>4</v>
       </c>
       <c r="C6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>5</v>
       </c>
@@ -460,15 +488,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>6</v>
       </c>
       <c r="C8" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>7</v>
       </c>
@@ -476,7 +504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>8</v>
       </c>
@@ -484,15 +512,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:3" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>10</v>
       </c>
@@ -500,12 +528,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>11</v>
       </c>
       <c r="C13" s="1" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
